--- a/daddy_cards.xlsx
+++ b/daddy_cards.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\super\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\daddy_card\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A82DB4D-B3BF-4F71-80F1-9E8AF06B780D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAE8E23-CD87-4A60-9019-5960C8F71107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{C2F67418-C11D-4363-8AC0-B948308EF2B3}"/>
   </bookViews>
@@ -1722,9 +1722,6 @@
   </si>
   <si>
     <t>파리지옥 놀이</t>
-  </si>
-  <si>
-    <t>🀀󟰼/p&gt;</t>
   </si>
   <si>
     <t>기어오는 아이를 팔로 가뒀다가 탈출하게 도와주기</t>
@@ -2086,6 +2083,10 @@
     <t>아빠꿀팁</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>🌿</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2206,55 +2207,55 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2610,40 +2611,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -6307,8 +6308,8 @@
       <c r="D98" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="E98" s="6" t="s">
-        <v>468</v>
+      <c r="E98" s="7" t="s">
+        <v>495</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>16</v>
@@ -6326,10 +6327,10 @@
         <v>128</v>
       </c>
       <c r="K98" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="L98" s="6" t="s">
         <v>469</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
@@ -6343,10 +6344,10 @@
         <v>10</v>
       </c>
       <c r="D99" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="E99" s="6" t="s">
         <v>471</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>472</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>33</v>
@@ -6364,10 +6365,10 @@
         <v>123</v>
       </c>
       <c r="K99" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="L99" s="6" t="s">
         <v>473</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
@@ -6381,10 +6382,10 @@
         <v>10</v>
       </c>
       <c r="D100" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="E100" s="6" t="s">
         <v>475</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>476</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>7</v>
@@ -6402,10 +6403,10 @@
         <v>289</v>
       </c>
       <c r="K100" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="L100" s="6" t="s">
         <v>477</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -6419,10 +6420,10 @@
         <v>10</v>
       </c>
       <c r="D101" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="E101" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>480</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>33</v>
@@ -6440,66 +6441,71 @@
         <v>128</v>
       </c>
       <c r="K101" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="L101" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="L101" s="6" t="s">
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102" s="14">
+        <v>101</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="12" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" s="8">
-        <v>101</v>
-      </c>
-      <c r="B102" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="C102" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D102" s="9" t="s">
+      <c r="E102" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="F102" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I102" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J102" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K102" s="12" t="s">
         <v>484</v>
       </c>
-      <c r="F102" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G102" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H102" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="I102" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J102" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="K102" s="9" t="s">
+      <c r="L102" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="L102" s="11" t="s">
-        <v>486</v>
-      </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" s="13"/>
-      <c r="B103" s="14"/>
-      <c r="C103" s="14"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="15"/>
-      <c r="F103" s="16"/>
-      <c r="G103" s="17"/>
-      <c r="H103" s="16"/>
-      <c r="I103" s="17"/>
-      <c r="J103" s="16"/>
-      <c r="K103" s="14"/>
-      <c r="L103" s="16"/>
+      <c r="A103" s="15"/>
+      <c r="B103" s="13"/>
+      <c r="C103" s="13"/>
+      <c r="D103" s="13"/>
+      <c r="E103" s="17"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="11"/>
+      <c r="H103" s="9"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="9"/>
+      <c r="K103" s="13"/>
+      <c r="L103" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="E102:E103"/>
     <mergeCell ref="L102:L103"/>
     <mergeCell ref="F102:F103"/>
     <mergeCell ref="G102:G103"/>
@@ -6507,11 +6513,6 @@
     <mergeCell ref="I102:I103"/>
     <mergeCell ref="J102:J103"/>
     <mergeCell ref="K102:K103"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="E102:E103"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
